--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2025/202511/Category_P&L_20251107.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AssetCategory/2025/202511/Category_P&L_20251107.xlsx
@@ -38077,19 +38077,19 @@
         <v>45968</v>
       </c>
       <c r="B992">
-        <v>82851817.20999999</v>
+        <v>106875110</v>
       </c>
       <c r="C992">
-        <v>35233.88</v>
+        <v>35328.68</v>
       </c>
       <c r="D992">
-        <v>0.00033</v>
+        <v>0.000331</v>
       </c>
       <c r="E992">
-        <v>-31497</v>
+        <v>-16901</v>
       </c>
       <c r="F992">
-        <v>-0.000295</v>
+        <v>-0.000159</v>
       </c>
       <c r="G992">
         <v>239421.71</v>
